--- a/kijoo/자료조사 kijoo.xlsx
+++ b/kijoo/자료조사 kijoo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AIservice\kijoo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5484BB-FCB7-49EF-8122-54C621991840}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8656AC11-3F4E-4201-9851-BB52A57777F0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9564" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="209">
   <si>
     <t>서비스 이름</t>
   </si>
@@ -405,6 +405,252 @@
   <si>
     <t>자동화 툴</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PromptBase</t>
+  </si>
+  <si>
+    <t>프롬프트 서비스</t>
+  </si>
+  <si>
+    <t>DALL-E, Midjourney, ChatGPT 등 주요 생성형 AI 프롬프트를 사고파는 마켓플레이스</t>
+  </si>
+  <si>
+    <t>https://promptbase.com</t>
+  </si>
+  <si>
+    <t>프롬프트 건당 개별 구매(주로 $2.99~$9.99), 판매자 수수료 20% (구독 시 수수료 할인)</t>
+  </si>
+  <si>
+    <t>검증된 고품질 프롬프트 결과물 미리보기가 가능하며 즉시 상용 수준의 프롬프트를 확보할 수 있음</t>
+  </si>
+  <si>
+    <t>단건 구매 비용이 누적될 수 있고 단순 프롬프트의 경우 직접 작성하는 것에 비해 효율이 떨어질 수 있음</t>
+  </si>
+  <si>
+    <t>특정 그림체·캐릭터 일관성 유지가 필요한 이미지 생성 및 정형화된 비즈니스 프롬프트 구매</t>
+  </si>
+  <si>
+    <t>디자인 작업 시 원하는 스타일의 키워드 조합을 빠르게 찾을 수 있어 시행착오를 대폭 줄여줌</t>
+  </si>
+  <si>
+    <t>PromptPerfect</t>
+  </si>
+  <si>
+    <t>거대언어모델 및 이미지 모델에 맞춰 입력된 프롬프트를 자동으로 최적화·고도화해주는 툴</t>
+  </si>
+  <si>
+    <t>https://promptperfect.xyz</t>
+  </si>
+  <si>
+    <t>Free(일일 기본 요청 제공), Standard $9.50/월, Pro $19.99/월, Pro Max $99.99/월</t>
+  </si>
+  <si>
+    <t>ChatGPT, Claude, Midjourney 등 타깃 모델별 최적의 구조로 자동 변환 및 다중 모델 비교 테스트 가능</t>
+  </si>
+  <si>
+    <t>초보자 수준의 짧은 문맥에서는 효과적이나 고도로 전문화된 도메인 프롬프트는 직접 튜닝이 여전히 필요함</t>
+  </si>
+  <si>
+    <t>초기 아이디어 프롬프트의 품질 향상 및 다중 LLM 간 프롬프트 성능 벤치마킹</t>
+  </si>
+  <si>
+    <t>모호하게 적은 문장도 모델이 이해하기 쉬운 명확한 지시문으로 즉각 다듬어주어 생산성이 올라감</t>
+  </si>
+  <si>
+    <t>FlowGPT</t>
+  </si>
+  <si>
+    <t>전 세계 사용자들이 공유한 방대한 오픈 프롬프트와 AI 캐릭터/에이전트를 직접 실행하는 커뮤니티</t>
+  </si>
+  <si>
+    <t>https://flowgpt.com</t>
+  </si>
+  <si>
+    <t>기본 무료(공개 프롬프트 실행), Plus $14.99/월, Ultra $24.99/월 (고급 모델 무제한 및 월간 Flux 지급)</t>
+  </si>
+  <si>
+    <t>실시간으로 프롬프트를 웹상에서 즉시 테스트해볼 수 있으며 게임, 업무, 롤플레잉 등 공유된 자산이 방대함</t>
+  </si>
+  <si>
+    <t>공개 커뮤니티 특성상 프롬프트의 완성도 편차가 크며 엔터테인먼트성 콘텐츠 비중이 높음</t>
+  </si>
+  <si>
+    <t>다양한 실무 및 창작용 프롬프트 템플릿 탐색, 웹 환경에서의 프롬프트 즉각 시뮬레이션</t>
+  </si>
+  <si>
+    <t>따로 API나 유료 구독 없이도 다른 사람들이 연구한 유용한 프롬프트를 브라우저에서 바로 써볼 수 있어 유용함</t>
+  </si>
+  <si>
+    <t>PromptHub</t>
+  </si>
+  <si>
+    <t>팀 단위로 프롬프트 버전을 관리하고 협업 및 테스트를 수행하는 엔지니어링 관리 플랫폼</t>
+  </si>
+  <si>
+    <t>https://www.prompthub.us</t>
+  </si>
+  <si>
+    <t>Free(월 2,000회 요청, 퍼블릭), Pro $12/월(연간 $9/월), Team 좌석당 $20/월, Enterprise 견적</t>
+  </si>
+  <si>
+    <t>Git 형태의 프롬프트 버전 제어, 배치 테스트, 팀원 간 프롬프트 검토 및 API 연동 지원</t>
+  </si>
+  <si>
+    <t>개인 단발성 작업보다는 개발 및 협업 중심이라 단순 프롬프트 수집 용도로는 과도한 구성임</t>
+  </si>
+  <si>
+    <t>사내 AI 서비스 개발 시 프롬프트 버전 관리, 팀 내 표준 프롬프트 라이브러리 운영</t>
+  </si>
+  <si>
+    <t>개발팀과 비개발팀이 함께 프롬프트 버전을 공유하고 모델별 응답 차이를 체계적으로 비교하기에 좋음</t>
+  </si>
+  <si>
+    <t>God of Prompt</t>
+  </si>
+  <si>
+    <t>마케팅, 영업, 코딩 등 업무 직무별로 고도화된 메가 프롬프트 팩과 템플릿을 제공하는 전문 허브</t>
+  </si>
+  <si>
+    <t>https://godofprompt.ai</t>
+  </si>
+  <si>
+    <t>무료 프롬프트 라이브러리 일부 제공, 올인원 번들 패키지 $97~$150 내외(평생 라이선스 형태)</t>
+  </si>
+  <si>
+    <t>단순 키워드가 아닌 실무 워크플로우 전체를 커버하는 체계적인 다단계 '메가 프롬프트' 구성</t>
+  </si>
+  <si>
+    <t>번들 구매 형태 위주라 초기 비용이 들며 모든 프롬프트가 개별 사용자의 업무와 100% 일치하지는 않음</t>
+  </si>
+  <si>
+    <t>마케팅 기획, 카피라이팅, SNS 전략 등 실제 비즈니스 프로세스에 즉시 투입 가능한 프롬프트 구축</t>
+  </si>
+  <si>
+    <t>실무에 필요한 단계별 지시문이 템플릿화되어 있어 복사해서 변수만 바꿔 넣어도 완성도가 높음</t>
+  </si>
+  <si>
+    <t>Cursor</t>
+  </si>
+  <si>
+    <t>바이브코딩</t>
+  </si>
+  <si>
+    <t>VS Code 기반에 Claude·GPT 등 최신 AI 모델을 네이티브로 통합한 대표적인 AI 코드 에디터</t>
+  </si>
+  <si>
+    <t>https://www.cursor.com</t>
+  </si>
+  <si>
+    <t>Hobby 무료(기본 요청), Pro $20/월(무제한 Fast 프리미엄 요청 등), Business 좌석당 $40/월</t>
+  </si>
+  <si>
+    <t>전체 코드베이스(@codebase)를 완벽히 인덱싱하여 다중 파일 수정 및 실시간 에러 디버깅 능력이 압도적임</t>
+  </si>
+  <si>
+    <t>사용량이 많을 경우 월 $20 구독 외에 고성능 모델 추가 요청 시 속도 제한 또는 추가 과금이 발생할 수 있음</t>
+  </si>
+  <si>
+    <t>자연어로 프로젝트 전체 아키텍처를 설계하고 빠르게 기능을 구현·수정하는 풀스택 바이브코딩</t>
+  </si>
+  <si>
+    <t>복잡한 코드 파악부터 다중 파일 동시 수정까지 개발 속도를 체감상 몇 배 이상 끌어올려 줌</t>
+  </si>
+  <si>
+    <t>v0 by Vercel</t>
+  </si>
+  <si>
+    <t>자연어 프롬프트나 스크린샷으로 React·Next.js 기반 고품질 UI 및 웹 컴포넌트를 즉시 코딩·배포하는 툴</t>
+  </si>
+  <si>
+    <t>https://v0.dev</t>
+  </si>
+  <si>
+    <t>Free(월 기본 200크레딧), Premium $20/월(5,000크레딧 및 초과 시 사용량 과금), Enterprise 맞춤 견적</t>
+  </si>
+  <si>
+    <t>Tailwind CSS와 shadcn/ui 기반의 세련된 UI 코드를 즉각 시각적 프리뷰로 확인하고 Vercel로 원클릭 배포 가능</t>
+  </si>
+  <si>
+    <t>프론트엔드 및 UI 구성에 최적화되어 있어 복잡한 백엔드 로직이나 데이터베이스 연동은 별도 코딩이 필요함</t>
+  </si>
+  <si>
+    <t>웹 프로토타입 빠른 제작, 랜딩 페이지 및 대시보드 UI 인터페이스를 시각적으로 찍어내는 바이브코딩</t>
+  </si>
+  <si>
+    <t>머릿속 디자인을 말로 설명하거나 대충 그린 스케치만 던져줘도 상용 수준의 컴포넌트를 즉시 뽑아냄</t>
+  </si>
+  <si>
+    <t>Bolt.new (StackBlitz)</t>
+  </si>
+  <si>
+    <t>브라우저 내 WebContainers 환경에서 프론트와 백엔드 풀스택 앱을 즉시 프롬프트로 빌드·실행·배포하는 서비스</t>
+  </si>
+  <si>
+    <t>https://bolt.new</t>
+  </si>
+  <si>
+    <t>Free(일일 기본 토큰), Pro $20/월(1,000만 토큰/월), Team $30/좌석/월</t>
+  </si>
+  <si>
+    <t>로컬 개발 환경 설정 없이 웹 브라우저 안에서 패키지 설치부터 서버 실행, 데이터베이스 연동까지 한 번에 완료됨</t>
+  </si>
+  <si>
+    <t>프로젝트 규모가 커질수록 컨텍스트 토큰 소모가 빠르며 복잡한 에러 발생 시 수동 디버깅이 까다로울 수 있음</t>
+  </si>
+  <si>
+    <t>아이디어 구상 단계에서 완벽히 작동하는 풀스택 웹 애플리케이션 프로토타입을 몇 분 만에 구현할 때</t>
+  </si>
+  <si>
+    <t>터미널 명령어까지 AI가 브라우저 가상머신에서 알아서 실행해주므로 환경 설정 스트레스 없이 바로 앱이 나옴</t>
+  </si>
+  <si>
+    <t>Replit (Replit Agent)</t>
+  </si>
+  <si>
+    <t>자연어 지시 한 번으로 기획부터 개발, DB 구축, 원클릭 클라우드 배포까지 자율 수행하는 AI 코딩 에이전트</t>
+  </si>
+  <si>
+    <t>https://replit.com</t>
+  </si>
+  <si>
+    <t>Starter 무료, Core $20/월(연간 $15/월, 에이전트 크레딧 포함), 팀 및 사용량 추가 과금</t>
+  </si>
+  <si>
+    <t>아이디어 설명만으로 데이터베이스, 인증, 백엔드 API, 배포 URL까지 포함된 완제품 소프트웨어를 스스로 완성함</t>
+  </si>
+  <si>
+    <t>에이전트 모드 사용 시 체크포인트마다 크레딧 소모가 빠르며 복잡한 커스텀 아키텍처에서는 지시를 정교하게 줘야 함</t>
+  </si>
+  <si>
+    <t>코딩 배경지식 없이도 자연어 대화만으로 실제 서비스 가능한 웹/모바일 앱을 원스톱으로 만들고 싶을 때</t>
+  </si>
+  <si>
+    <t>개발 전 과정을 자율 주행처럼 알아서 처리해주므로 비개발자도 온전한 서비스 하나를 뚝딱 배포할 수 있음</t>
+  </si>
+  <si>
+    <t>Windsurf (Codeium)</t>
+  </si>
+  <si>
+    <t>개발자의 행동 흐름을 실시간으로 추적·동기화하는 'Flows' 엔진 기반의 차세대 AI 네이티브 IDE</t>
+  </si>
+  <si>
+    <t>https://codeium.com/windsurf</t>
+  </si>
+  <si>
+    <t>Free(기본 쿼리 제공), Pro $15/월(무제한 Flow 및 프리미엄 모델), Enterprise 별도 견적</t>
+  </si>
+  <si>
+    <t>개발자가 코드를 만지는 맥락을 실시간으로 파악하여 터미널과 에디터를 넘나들며 유기적으로 협업함 (가성비 우수)</t>
+  </si>
+  <si>
+    <t>Cursor 대비 플러그인 생태계와 사용자 커뮤니티 규모가 아직 성장 중인 단계임</t>
+  </si>
+  <si>
+    <t>Cursor의 훌륭한 대안으로, 보다 매끄러운 컨텍스트 전환과 합리적인 비용으로 바이브코딩 환경을 구축할 때</t>
+  </si>
+  <si>
+    <t>터미널 에러를 AI가 스스로 감지하고 고쳐주는 유기적인 흐름이 매우 자연스러워 코딩 몰입도가 높음</t>
   </si>
 </sst>
 </file>
@@ -1356,7 +1602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="26.09765625" bestFit="1" customWidth="1"/>
@@ -1826,6 +2072,296 @@
         <v>125</v>
       </c>
     </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" t="s">
+        <v>130</v>
+      </c>
+      <c r="E18" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" t="s">
+        <v>132</v>
+      </c>
+      <c r="G18" t="s">
+        <v>133</v>
+      </c>
+      <c r="H18" t="s">
+        <v>134</v>
+      </c>
+      <c r="I18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" t="s">
+        <v>139</v>
+      </c>
+      <c r="F19" t="s">
+        <v>140</v>
+      </c>
+      <c r="G19" t="s">
+        <v>141</v>
+      </c>
+      <c r="H19" t="s">
+        <v>142</v>
+      </c>
+      <c r="I19" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" t="s">
+        <v>146</v>
+      </c>
+      <c r="E20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F20" t="s">
+        <v>148</v>
+      </c>
+      <c r="G20" t="s">
+        <v>149</v>
+      </c>
+      <c r="H20" t="s">
+        <v>150</v>
+      </c>
+      <c r="I20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" t="s">
+        <v>153</v>
+      </c>
+      <c r="D21" t="s">
+        <v>154</v>
+      </c>
+      <c r="E21" t="s">
+        <v>155</v>
+      </c>
+      <c r="F21" t="s">
+        <v>156</v>
+      </c>
+      <c r="G21" t="s">
+        <v>157</v>
+      </c>
+      <c r="H21" t="s">
+        <v>158</v>
+      </c>
+      <c r="I21" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>160</v>
+      </c>
+      <c r="B22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" t="s">
+        <v>161</v>
+      </c>
+      <c r="D22" t="s">
+        <v>162</v>
+      </c>
+      <c r="E22" t="s">
+        <v>163</v>
+      </c>
+      <c r="F22" t="s">
+        <v>164</v>
+      </c>
+      <c r="G22" t="s">
+        <v>165</v>
+      </c>
+      <c r="H22" t="s">
+        <v>166</v>
+      </c>
+      <c r="I22" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>168</v>
+      </c>
+      <c r="B23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C23" t="s">
+        <v>170</v>
+      </c>
+      <c r="D23" t="s">
+        <v>171</v>
+      </c>
+      <c r="E23" t="s">
+        <v>172</v>
+      </c>
+      <c r="F23" t="s">
+        <v>173</v>
+      </c>
+      <c r="G23" t="s">
+        <v>174</v>
+      </c>
+      <c r="H23" t="s">
+        <v>175</v>
+      </c>
+      <c r="I23" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B24" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" t="s">
+        <v>178</v>
+      </c>
+      <c r="D24" t="s">
+        <v>179</v>
+      </c>
+      <c r="E24" t="s">
+        <v>180</v>
+      </c>
+      <c r="F24" t="s">
+        <v>181</v>
+      </c>
+      <c r="G24" t="s">
+        <v>182</v>
+      </c>
+      <c r="H24" t="s">
+        <v>183</v>
+      </c>
+      <c r="I24" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>185</v>
+      </c>
+      <c r="B25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" t="s">
+        <v>186</v>
+      </c>
+      <c r="D25" t="s">
+        <v>187</v>
+      </c>
+      <c r="E25" t="s">
+        <v>188</v>
+      </c>
+      <c r="F25" t="s">
+        <v>189</v>
+      </c>
+      <c r="G25" t="s">
+        <v>190</v>
+      </c>
+      <c r="H25" t="s">
+        <v>191</v>
+      </c>
+      <c r="I25" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>193</v>
+      </c>
+      <c r="B26" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" t="s">
+        <v>194</v>
+      </c>
+      <c r="D26" t="s">
+        <v>195</v>
+      </c>
+      <c r="E26" t="s">
+        <v>196</v>
+      </c>
+      <c r="F26" t="s">
+        <v>197</v>
+      </c>
+      <c r="G26" t="s">
+        <v>198</v>
+      </c>
+      <c r="H26" t="s">
+        <v>199</v>
+      </c>
+      <c r="I26" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>201</v>
+      </c>
+      <c r="B27" t="s">
+        <v>169</v>
+      </c>
+      <c r="C27" t="s">
+        <v>202</v>
+      </c>
+      <c r="D27" t="s">
+        <v>203</v>
+      </c>
+      <c r="E27" t="s">
+        <v>204</v>
+      </c>
+      <c r="F27" t="s">
+        <v>205</v>
+      </c>
+      <c r="G27" t="s">
+        <v>206</v>
+      </c>
+      <c r="H27" t="s">
+        <v>207</v>
+      </c>
+      <c r="I27" t="s">
+        <v>208</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{9A33205E-DC14-4D4E-AABE-AE049ADA6BB7}"/>
   <phoneticPr fontId="18" type="noConversion"/>

--- a/kijoo/자료조사 kijoo.xlsx
+++ b/kijoo/자료조사 kijoo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AIservice\kijoo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8656AC11-3F4E-4201-9851-BB52A57777F0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E890E9-8E88-47D6-8A0F-A6EEDBB25CF8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9564" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="426">
   <si>
     <t>서비스 이름</t>
   </si>
@@ -651,13 +651,665 @@
   </si>
   <si>
     <t>터미널 에러를 AI가 스스로 감지하고 고쳐주는 유기적인 흐름이 매우 자연스러워 코딩 몰입도가 높음</t>
+  </si>
+  <si>
+    <t>Gamma</t>
+  </si>
+  <si>
+    <t>시각화/PPT</t>
+  </si>
+  <si>
+    <t>프롬프트 한 줄로 발표 자료 생성</t>
+  </si>
+  <si>
+    <t>https://gamma.app</t>
+  </si>
+  <si>
+    <t>부분 무료</t>
+  </si>
+  <si>
+    <t>생성 속도가 빠르고 웹페이지·문서 형태로도 만듦</t>
+  </si>
+  <si>
+    <t>무료 크레딧이 적고 PPTX로 내보내면 레이아웃이 깨질 수 있음</t>
+  </si>
+  <si>
+    <t>빠른 초안, 과제 발표</t>
+  </si>
+  <si>
+    <t>PPT 자동 생성</t>
+  </si>
+  <si>
+    <t>미리캔버스 AI 프레젠테이션</t>
+  </si>
+  <si>
+    <t>주제·PDF·텍스트로 PPT 자동 생성</t>
+  </si>
+  <si>
+    <t>https://miricanvas.com</t>
+  </si>
+  <si>
+    <t>한국 감성 템플릿, PPTX 내보내기</t>
+  </si>
+  <si>
+    <t>AI 생성 결과의 내용 깊이가 얕아 직접 보완이 필요하고, 고급 템플릿은 유료</t>
+  </si>
+  <si>
+    <t>국내 학교·회사 발표</t>
+  </si>
+  <si>
+    <t>Canva AI</t>
+  </si>
+  <si>
+    <t>AI와 대화하며 디자인 PPT 완성</t>
+  </si>
+  <si>
+    <t>https://canva.com</t>
+  </si>
+  <si>
+    <t>템플릿이 아주 많고 브랜드 스타일 자동 적용</t>
+  </si>
+  <si>
+    <t>AI 생성 슬라이드의 내용이 일반적이고, 프리미엄 요소는 유료</t>
+  </si>
+  <si>
+    <t>디자인이 중요한 발표, SNS 겸용</t>
+  </si>
+  <si>
+    <t>Kivo</t>
+  </si>
+  <si>
+    <t>원하는 디자인 레퍼런스를 고르면 그 스타일로 발표 자료 전체를 만들어 주는 AI</t>
+  </si>
+  <si>
+    <t>https://kivo.art</t>
+  </si>
+  <si>
+    <t>레퍼런스 기반 8가지 디자인 시안 제공, 전 슬라이드 디자인 통일, 피그마처럼 세밀한 편집, 이미지·PPTX·PDF 내보내기</t>
+  </si>
+  <si>
+    <t>무료 크레딧이 적고 디자인이 제공된 레퍼런스 스타일 안에서만 고를 수 있음</t>
+  </si>
+  <si>
+    <t>디자인 완성도가 중요한 발표·피치덱</t>
+  </si>
+  <si>
+    <t>Beautiful.ai</t>
+  </si>
+  <si>
+    <t>내용을 넣으면 레이아웃이 자동 정렬되는 슬라이드</t>
+  </si>
+  <si>
+    <t>https://beautiful.ai</t>
+  </si>
+  <si>
+    <t>유료(체험판)</t>
+  </si>
+  <si>
+    <t>디자인이 흐트러지지 않음</t>
+  </si>
+  <si>
+    <t>무료 플랜이 없고, 자동 레이아웃 때문에 세밀한 자유 배치가 어려움</t>
+  </si>
+  <si>
+    <t>회사 보고서, 정돈된 비즈니스 덱</t>
+  </si>
+  <si>
+    <t>Pitch</t>
+  </si>
+  <si>
+    <t>팀 협업형 프레젠테이션 도구</t>
+  </si>
+  <si>
+    <t>https://pitch.com</t>
+  </si>
+  <si>
+    <t>실시간 공동 편집</t>
+  </si>
+  <si>
+    <t>한국어 템플릿이 적고, AI 생성 기능이 비교적 단순함</t>
+  </si>
+  <si>
+    <t>스타트업 피치덱, 팀 프로젝트</t>
+  </si>
+  <si>
+    <t>Prezi AI</t>
+  </si>
+  <si>
+    <t>화면 이동·확대식 비선형 발표 생성</t>
+  </si>
+  <si>
+    <t>https://prezi.com</t>
+  </si>
+  <si>
+    <t>독특한 애니메이션</t>
+  </si>
+  <si>
+    <t>비선형 구조에 익숙해지기까지 시간이 걸리고, PPTX 호환이 약함</t>
+  </si>
+  <si>
+    <t>강의, 스토리텔링 발표</t>
+  </si>
+  <si>
+    <t>Genspark AI Slides</t>
+  </si>
+  <si>
+    <t>웹 검색으로 자료를 조사한 뒤 슬라이드 생성</t>
+  </si>
+  <si>
+    <t>https://genspark.ai</t>
+  </si>
+  <si>
+    <t>리서치와 제작을 한 번에, 다양한 내보내기</t>
+  </si>
+  <si>
+    <t>크레딧 소모가 빠르고, 조사 내용의 출처를 직접 검증해야 함</t>
+  </si>
+  <si>
+    <t>조사 기반 발표</t>
+  </si>
+  <si>
+    <t>Presentations.AI</t>
+  </si>
+  <si>
+    <t>텍스트·문서로 빠르게 덱 생성</t>
+  </si>
+  <si>
+    <t>https://presentations.ai</t>
+  </si>
+  <si>
+    <t>내용 정확도가 괜찮고 빠름</t>
+  </si>
+  <si>
+    <t>디자인 선택지가 제한적이고, 무료 플랜 내보내기에 제약이 있음</t>
+  </si>
+  <si>
+    <t>일반 업무 발표</t>
+  </si>
+  <si>
+    <t>Decktopus</t>
+  </si>
+  <si>
+    <t>질문에 답하면 초안을 만들어 주는 도구</t>
+  </si>
+  <si>
+    <t>https://decktopus.com</t>
+  </si>
+  <si>
+    <t>백지에서 시작하기 쉬움</t>
+  </si>
+  <si>
+    <t>한국어 지원이 약하고, 디자인이 단조로운 편</t>
+  </si>
+  <si>
+    <t>발표 초보자</t>
+  </si>
+  <si>
+    <t>Storydoc</t>
+  </si>
+  <si>
+    <t>스크롤형 인터랙티브 프레젠테이션</t>
+  </si>
+  <si>
+    <t>https://storydoc.com</t>
+  </si>
+  <si>
+    <t>웹처럼 읽히는 덱</t>
+  </si>
+  <si>
+    <t>가격이 비싸고, 일반 PPT 파일로 쓰기 어려움</t>
+  </si>
+  <si>
+    <t>제안서, 영업 자료</t>
+  </si>
+  <si>
+    <t>Presenti AI</t>
+  </si>
+  <si>
+    <t>상호작용형 발표 생성</t>
+  </si>
+  <si>
+    <t>https://presenti.ai</t>
+  </si>
+  <si>
+    <t>실시간 투표·퀴즈 기능</t>
+  </si>
+  <si>
+    <t>인지도가 낮아 자료가 적고, 한국어 결과물 품질이 불안정함</t>
+  </si>
+  <si>
+    <t>수업, 참여형 발표</t>
+  </si>
+  <si>
+    <t>Slidesgo AI</t>
+  </si>
+  <si>
+    <t>템플릿 기반 빠른 생성</t>
+  </si>
+  <si>
+    <t>https://slidesgo.com</t>
+  </si>
+  <si>
+    <t>무료 템플릿이 풍부함</t>
+  </si>
+  <si>
+    <t>AI 생성 내용이 단순하고, 무료 템플릿 사용 시 출처 표기 필요</t>
+  </si>
+  <si>
+    <t>학생 과제</t>
+  </si>
+  <si>
+    <t>MagicSlides</t>
+  </si>
+  <si>
+    <t>텍스트·PDF·영상으로 슬라이드 생성</t>
+  </si>
+  <si>
+    <t>https://magicslides.app</t>
+  </si>
+  <si>
+    <t>가볍고 단순함</t>
+  </si>
+  <si>
+    <t>디자인 퀄리티가 평범하고, 무료 사용 횟수가 적음</t>
+  </si>
+  <si>
+    <t>강의 요약 슬라이드</t>
+  </si>
+  <si>
+    <t>Microsoft Copilot (PowerPoint)</t>
+  </si>
+  <si>
+    <t>PowerPoint에 내장된 AI</t>
+  </si>
+  <si>
+    <t>https://microsoft.com/microsoft-365/copilot</t>
+  </si>
+  <si>
+    <t>유료(M365)</t>
+  </si>
+  <si>
+    <t>처음부터 PPT 형식이라 변환할 필요 없음</t>
+  </si>
+  <si>
+    <t>M365 유료 구독이 필요하고, 생성 품질이 원본 자료에 크게 좌우됨</t>
+  </si>
+  <si>
+    <t>회사 PPT 작업</t>
+  </si>
+  <si>
+    <t>PPT 프로그램 내장 AI</t>
+  </si>
+  <si>
+    <t>Gemini in Google Slides</t>
+  </si>
+  <si>
+    <t>구글 슬라이드 안의 AI</t>
+  </si>
+  <si>
+    <t>https://workspace.google.com</t>
+  </si>
+  <si>
+    <t>요금제에 따라 다름</t>
+  </si>
+  <si>
+    <t>구글 드라이브·문서와 연동</t>
+  </si>
+  <si>
+    <t>워크스페이스 유료 요금제가 필요하고, 슬라이드 생성 기능이 아직 제한적</t>
+  </si>
+  <si>
+    <t>구글 워크스페이스 사용자</t>
+  </si>
+  <si>
+    <t>Plus AI</t>
+  </si>
+  <si>
+    <t>Google Slides·PowerPoint용 AI 애드온</t>
+  </si>
+  <si>
+    <t>https://plusdocs.com</t>
+  </si>
+  <si>
+    <t>기존 템플릿에 맞춰 생성·리믹스</t>
+  </si>
+  <si>
+    <t>무료 플랜이 없고, 한국어 결과물 품질이 영어보다 떨어짐</t>
+  </si>
+  <si>
+    <t>전문 발표 제작자</t>
+  </si>
+  <si>
+    <t>SlidesAI</t>
+  </si>
+  <si>
+    <t>Google Slides 애드온형 생성기</t>
+  </si>
+  <si>
+    <t>https://slidesai.io</t>
+  </si>
+  <si>
+    <t>익숙한 환경을 그대로 사용</t>
+  </si>
+  <si>
+    <t>무료 생성 횟수가 매우 적고, 디자인 선택지가 제한적</t>
+  </si>
+  <si>
+    <t>구글 슬라이드 사용자</t>
+  </si>
+  <si>
+    <t>Napkin AI</t>
+  </si>
+  <si>
+    <t>글을 붙여넣으면 도식·인포그래픽으로 변환</t>
+  </si>
+  <si>
+    <t>https://napkin.ai</t>
+  </si>
+  <si>
+    <t>편집 가능한 결과물, 여러 형식으로 내보내기</t>
+  </si>
+  <si>
+    <t>PPT 전체가 아닌 도식 위주이며, 무료 플랜은 워터마크·크레딧 제한</t>
+  </si>
+  <si>
+    <t>보고서·PPT 속 도식</t>
+  </si>
+  <si>
+    <t>다이어그램·인포그래픽</t>
+  </si>
+  <si>
+    <t>Piktochart AI</t>
+  </si>
+  <si>
+    <t>인포그래픽·리포트 특화 디자인 도구</t>
+  </si>
+  <si>
+    <t>https://piktochart.com</t>
+  </si>
+  <si>
+    <t>데이터가 많은 자료를 깔끔하게 정리</t>
+  </si>
+  <si>
+    <t>AI 기능이 기본 수준이고, 무료 플랜은 다운로드 형식·워터마크 제한</t>
+  </si>
+  <si>
+    <t>인포그래픽, 연구 결과 발표</t>
+  </si>
+  <si>
+    <t>Visme AI</t>
+  </si>
+  <si>
+    <t>인포그래픽·차트·발표 통합 도구</t>
+  </si>
+  <si>
+    <t>https://visme.co</t>
+  </si>
+  <si>
+    <t>차트와 디자인 요소가 풍부함</t>
+  </si>
+  <si>
+    <t>기능이 많아 처음엔 복잡하고, 무료 플랜 제약이 큼</t>
+  </si>
+  <si>
+    <t>마케팅 자료</t>
+  </si>
+  <si>
+    <t>Whimsical AI</t>
+  </si>
+  <si>
+    <t>마인드맵·플로우차트 자동 생성</t>
+  </si>
+  <si>
+    <t>https://whimsical.com</t>
+  </si>
+  <si>
+    <t>결과물이 깔끔하고 빠름</t>
+  </si>
+  <si>
+    <t>무료 플랜은 AI 사용 횟수·보드 수 제한, 한국어 자료 적음</t>
+  </si>
+  <si>
+    <t>아이디어 정리, 서비스 흐름도</t>
+  </si>
+  <si>
+    <t>Miro AI</t>
+  </si>
+  <si>
+    <t>협업 화이트보드 + AI 다이어그램</t>
+  </si>
+  <si>
+    <t>https://miro.com</t>
+  </si>
+  <si>
+    <t>다른 도구 연동이 많고 실시간 협업</t>
+  </si>
+  <si>
+    <t>보드가 커지면 무거워지고, AI 크레딧이 제한적</t>
+  </si>
+  <si>
+    <t>팀 브레인스토밍</t>
+  </si>
+  <si>
+    <t>Lucidchart AI</t>
+  </si>
+  <si>
+    <t>정확한 구조도·순서도 생성</t>
+  </si>
+  <si>
+    <t>https://lucidchart.com</t>
+  </si>
+  <si>
+    <t>기술 문서 수준의 정밀함</t>
+  </si>
+  <si>
+    <t>무료 플랜은 문서·도형 수 제한이 크고, 학습 곡선이 있음</t>
+  </si>
+  <si>
+    <t>조직도, 업무 프로세스</t>
+  </si>
+  <si>
+    <t>Eraser</t>
+  </si>
+  <si>
+    <t>기술 아키텍처 다이어그램 + 코드형 편집</t>
+  </si>
+  <si>
+    <t>https://eraser.io</t>
+  </si>
+  <si>
+    <t>다이어그램을 텍스트 코드로 수정</t>
+  </si>
+  <si>
+    <t>개발자 대상이라 비개발자에겐 어렵고, 무료 AI 사용량 제한</t>
+  </si>
+  <si>
+    <t>개발 문서, 시스템 구조도</t>
+  </si>
+  <si>
+    <t>Mermaid Chart</t>
+  </si>
+  <si>
+    <t>자연어를 Mermaid 다이어그램 코드로 변환</t>
+  </si>
+  <si>
+    <t>https://mermaidchart.com</t>
+  </si>
+  <si>
+    <t>코드로 관리하기 쉬움</t>
+  </si>
+  <si>
+    <t>Mermaid 문법을 알아야 수정이 편하고, 디자인 자유도가 낮음</t>
+  </si>
+  <si>
+    <t>개발자 문서</t>
+  </si>
+  <si>
+    <t>Xmind AI</t>
+  </si>
+  <si>
+    <t>AI 마인드맵 생성</t>
+  </si>
+  <si>
+    <t>https://xmind.ai</t>
+  </si>
+  <si>
+    <t>마인드맵 전문</t>
+  </si>
+  <si>
+    <t>마인드맵 외 용도로는 활용도가 낮고, 고급 기능은 유료</t>
+  </si>
+  <si>
+    <t>발표 목차 구상, 학습 정리</t>
+  </si>
+  <si>
+    <t>Julius AI</t>
+  </si>
+  <si>
+    <t>파일을 올리고 질문하면 분석 결과와 차트를 만들어 줌</t>
+  </si>
+  <si>
+    <t>https://julius.ai</t>
+  </si>
+  <si>
+    <t>코딩 없이 데이터 분석</t>
+  </si>
+  <si>
+    <t>무료 플랜 메시지 수가 적고, 분석 결과를 직접 검증해야 함</t>
+  </si>
+  <si>
+    <t>엑셀·CSV 데이터 시각화</t>
+  </si>
+  <si>
+    <t>데이터 시각화·차트</t>
+  </si>
+  <si>
+    <t>Power BI Copilot</t>
+  </si>
+  <si>
+    <t>Power BI 안의 AI 분석·보고서 생성</t>
+  </si>
+  <si>
+    <t>https://powerbi.microsoft.com</t>
+  </si>
+  <si>
+    <t>유료</t>
+  </si>
+  <si>
+    <t>기업 데이터와 연동</t>
+  </si>
+  <si>
+    <t>Premium/Fabric 등 고가 라이선스가 필요하고, 초기 설정이 복잡함</t>
+  </si>
+  <si>
+    <t>회사 대시보드</t>
+  </si>
+  <si>
+    <t>Tableau (Tableau AI)</t>
+  </si>
+  <si>
+    <t>전문 BI 시각화 도구의 AI 기능</t>
+  </si>
+  <si>
+    <t>https://tableau.com</t>
+  </si>
+  <si>
+    <t>차트를 세밀하게 다룰 수 있음</t>
+  </si>
+  <si>
+    <t>가격이 비싸고, 배우는 데 시간이 오래 걸림</t>
+  </si>
+  <si>
+    <t>전문 데이터 분석</t>
+  </si>
+  <si>
+    <t>ThoughtSpot</t>
+  </si>
+  <si>
+    <t>검색하듯 질문하면 차트가 나오는 BI 도구</t>
+  </si>
+  <si>
+    <t>https://thoughtspot.com</t>
+  </si>
+  <si>
+    <t>실시간 데이터 검색</t>
+  </si>
+  <si>
+    <t>기업용이라 개인이 쓰기 어렵고, 가격 정보가 불투명함</t>
+  </si>
+  <si>
+    <t>기업 데이터 조회</t>
+  </si>
+  <si>
+    <t>Claude</t>
+  </si>
+  <si>
+    <t>내용 구성부터 슬라이드·문서·차트·인터랙티브 웹페이지까지 만드는 AI</t>
+  </si>
+  <si>
+    <t>https://claude.ai</t>
+  </si>
+  <si>
+    <t>긴 자료를 정확하게 정리하고, 결과물을 공유 가능한 페이지로 생성</t>
+  </si>
+  <si>
+    <t>PPTX 파일을 바로 만들 때는 디자인 손질이 필요하고, 무료 플랜은 사용량 제한이 있음</t>
+  </si>
+  <si>
+    <t>발표 내용 구성, 데이터 차트, 시각 자료 제작</t>
+  </si>
+  <si>
+    <t>범용 AI 어시스턴트</t>
+  </si>
+  <si>
+    <t>ChatGPT</t>
+  </si>
+  <si>
+    <t>대화형 AI, 데이터 분석과 이미지 생성</t>
+  </si>
+  <si>
+    <t>https://chatgpt.com</t>
+  </si>
+  <si>
+    <t>엑셀 분석으로 차트를 만들고 이미지도 생성</t>
+  </si>
+  <si>
+    <t>생성한 이미지 속 한글 글자가 깨지는 경우가 있고, 무료 플랜은 사용량 제한</t>
+  </si>
+  <si>
+    <t>발표 대본, 간단한 차트</t>
+  </si>
+  <si>
+    <t>Gemini</t>
+  </si>
+  <si>
+    <t>구글의 AI 어시스턴트</t>
+  </si>
+  <si>
+    <t>https://gemini.google.com</t>
+  </si>
+  <si>
+    <t>구글 서비스와 연동</t>
+  </si>
+  <si>
+    <t>슬라이드 직접 생성은 제한적이고, 답변의 사실 여부를 검증해야 함</t>
+  </si>
+  <si>
+    <t>자료 조사 후 슬라이드 초안</t>
+  </si>
+  <si>
+    <t>https://kivo.art</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>무료 크레딧이 적고 디자인이 제공된 레퍼런스 스타일 안에서만 고를 수 있음,디자인 완성도가 중요한 발표·피치덱</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -812,6 +1464,15 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -1115,7 +1776,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1242,13 +1903,22 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1291,6 +1961,7 @@
     <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="42" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1602,7 +2273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="26.09765625" bestFit="1" customWidth="1"/>
@@ -2043,7 +2714,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>118</v>
       </c>
@@ -2072,7 +2743,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -2101,7 +2772,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>136</v>
       </c>
@@ -2130,7 +2801,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>144</v>
       </c>
@@ -2159,7 +2830,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>152</v>
       </c>
@@ -2188,7 +2859,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>160</v>
       </c>
@@ -2217,7 +2888,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>168</v>
       </c>
@@ -2246,7 +2917,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>177</v>
       </c>
@@ -2275,7 +2946,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>185</v>
       </c>
@@ -2304,7 +2975,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>193</v>
       </c>
@@ -2333,7 +3004,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>201</v>
       </c>
@@ -2360,12 +3031,1061 @@
       </c>
       <c r="I27" t="s">
         <v>208</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A28" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A29" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A30" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A31" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A32" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A33" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A34" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A35" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A36" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A37" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A38" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A39" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A40" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A41" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A42" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A43" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A44" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A45" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A46" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A47" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A48" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A49" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A50" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A51" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A52" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A53" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A54" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A55" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A56" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A57" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A58" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A59" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A60" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A61" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>230</v>
+      </c>
+      <c r="B62" t="s">
+        <v>210</v>
+      </c>
+      <c r="C62" t="s">
+        <v>231</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E62" t="s">
+        <v>213</v>
+      </c>
+      <c r="F62" t="s">
+        <v>233</v>
+      </c>
+      <c r="H62" t="s">
+        <v>425</v>
+      </c>
+      <c r="J62" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{9A33205E-DC14-4D4E-AABE-AE049ADA6BB7}"/>
   <phoneticPr fontId="18" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D62" r:id="rId1" xr:uid="{0E382258-CB96-41B8-8472-CF7481691F0C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/kijoo/자료조사 kijoo.xlsx
+++ b/kijoo/자료조사 kijoo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AIservice\kijoo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E890E9-8E88-47D6-8A0F-A6EEDBB25CF8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FCA38C3-8D84-48CF-970C-2ED0207AA8BA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9564" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'자료조사 양식'!$A$1:$I$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="662">
   <si>
     <t>서비스 이름</t>
   </si>
@@ -1298,18 +1298,725 @@
     <t>자료 조사 후 슬라이드 초안</t>
   </si>
   <si>
-    <t>https://kivo.art</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>무료 크레딧이 적고 디자인이 제공된 레퍼런스 스타일 안에서만 고를 수 있음,디자인 완성도가 중요한 발표·피치덱</t>
+    <t>ChatGPT Images (GPT Image)</t>
+  </si>
+  <si>
+    <t>이미지</t>
+  </si>
+  <si>
+    <t>대화형 프롬프트로 이미지를 만들고, 업로드한 이미지도 자연어로 수정하는 범용 이미지 AI</t>
+  </si>
+  <si>
+    <t>https://chatgpt.com/</t>
+  </si>
+  <si>
+    <t>무료+유료</t>
+  </si>
+  <si>
+    <t>새 계정 없이 바로 테스트 가능(현재 ChatGPT 사용자), 대화로 반복 수정이 쉬움, 텍스트·투명 배경·부분 편집 지원</t>
+  </si>
+  <si>
+    <t>복잡한 편집은 원치 않는 영역까지 바뀔 수 있고 사용량 제한이 요금제에 따라 다름</t>
+  </si>
+  <si>
+    <t>범용 이미지 생성, 기존 사진 편집, 포스터·썸네일, 빠른 반복 수정</t>
+  </si>
+  <si>
+    <t>사용이 쉽고 결과 생성이 빠르며, 원본 이미지를 유지하면서 원하는 부분만 자연스럽게 수정할수 있고 글자 표현도 정확함.</t>
+  </si>
+  <si>
+    <t>Gemini (Nano Banana / Nano Banana Pro)</t>
+  </si>
+  <si>
+    <t>Google의 Nano Banana 계열 모델로 대화형 이미지 생성·편집과 여러 참조 이미지 활용이 가능한 AI</t>
+  </si>
+  <si>
+    <t>https://gemini.google.com/</t>
+  </si>
+  <si>
+    <t>부분 편집·스타일 변경·다중 참조에 강하고, 복잡한 지시와 텍스트 포함 디자인에 유용</t>
+  </si>
+  <si>
+    <t>무료 한도 이후 모델이 전환되거나 사용량 제한이 생길 수 있음</t>
+  </si>
+  <si>
+    <t>사진 편집, 캐릭터/제품 일관성, 포스터·인포그래픽, 복합 이미지 구성</t>
+  </si>
+  <si>
+    <t>Google AI Studio (Nano Banana)</t>
+  </si>
+  <si>
+    <t>Gemini 이미지 모델을 직접 선택해 시험하고 API용 프롬프트까지 확인할 수 있는 개발자용 플레이그라운드</t>
+  </si>
+  <si>
+    <t>https://aistudio.google.com/</t>
+  </si>
+  <si>
+    <t>모델을 직접 선택해 비교 가능, 이미지+텍스트 입력과 반복 편집 테스트에 좋음</t>
+  </si>
+  <si>
+    <t>일반 사용자에게는 Gemini 앱보다 화면이 기술적이고 설정이 많음</t>
+  </si>
+  <si>
+    <t>모델 비교, 고급 프롬프트 실험, API 전 단계 테스트</t>
+  </si>
+  <si>
+    <t>Krea</t>
+  </si>
+  <si>
+    <t>실시간 생성, 여러 이미지 모델, 편집·업스케일·LoRA를 한곳에서 제공하는 크리에이티브 플랫폼</t>
+  </si>
+  <si>
+    <t>https://www.krea.ai/</t>
+  </si>
+  <si>
+    <t>실시간 생성이 빠르고 여러 모델을 한 화면에서 비교 가능, 편집·향상 기능이 풍부함</t>
+  </si>
+  <si>
+    <t>기능과 모델이 많아 처음에는 인터페이스가 복잡할 수 있고 고급 기능은 크레딧을 많이 사용</t>
+  </si>
+  <si>
+    <t>아이디어 스케치, 빠른 스타일 탐색, 업스케일, 여러 모델 비교</t>
+  </si>
+  <si>
+    <t>무료 사용시 Large 모델은 1회로 제한되는 토큰양을 가지고 있고 이후 Turbo 모델을 사용해야했음. 글자 깨짐과 원본 이미지 보존이 아쉬웠음. 토큰 소모가  큰편인데도 결과가 완벽하지 않았음.</t>
+  </si>
+  <si>
+    <t>Leonardo.Ai</t>
+  </si>
+  <si>
+    <t>텍스트 생성부터 AI 포토 에디터·실시간 캔버스까지 제공하는 올인원 이미지 제작 플랫폼</t>
+  </si>
+  <si>
+    <t>https://www.leonardo.ai/</t>
+  </si>
+  <si>
+    <t>생성/편집 기능이 한곳에 있고 다양한 모델·프리셋으로 결과를 세밀하게 조절 가능</t>
+  </si>
+  <si>
+    <t>토큰 구조와 옵션이 많아 초보자에게는 설정이 복잡하게 느껴질 수 있음</t>
+  </si>
+  <si>
+    <t>콘셉트 아트, 제품 이미지, 캐릭터, 반복 편집</t>
+  </si>
+  <si>
+    <t>Grok Imagine</t>
+  </si>
+  <si>
+    <t>xAI의 이미지 생성·편집 기능으로 자연어 지시와 부분 선택 기반 정밀 편집을 지원</t>
+  </si>
+  <si>
+    <t>https://grok.com/imagine</t>
+  </si>
+  <si>
+    <t>지시 준수와 텍스트/레이아웃, 특정 영역만 바꾸는 편집 기능이 강점</t>
+  </si>
+  <si>
+    <t>생성물에 Grok 워터마크가 포함될 수 있고 무료 한도는 제한적</t>
+  </si>
+  <si>
+    <t>포스터·레이아웃, 이미지 리터치, 요소 교체·삭제</t>
+  </si>
+  <si>
+    <t>Adobe Firefly</t>
+  </si>
+  <si>
+    <t>Adobe의 생성형 AI 공간으로 이미지 생성·오브젝트 제거·확장·업스케일과 파트너 모델을 함께 제공</t>
+  </si>
+  <si>
+    <t>https://firefly.adobe.com/</t>
+  </si>
+  <si>
+    <t>편집 도구가 직관적이고 Photoshop/Adobe 생태계와 연계가 좋으며 다양한 모델을 한곳에서 사용 가능</t>
+  </si>
+  <si>
+    <t>고급·프리미엄 모델은 크레딧을 사용하고 Adobe 계정 가입이 필요</t>
+  </si>
+  <si>
+    <t>광고 이미지, 제품 이미지, 배경 교체, 확장·오브젝트 제거</t>
+  </si>
+  <si>
+    <t>Adobe Photoshop (Generative Fill)</t>
+  </si>
+  <si>
+    <t>Photoshop의 선택·레이어 작업에 생성형 채우기와 확장을 결합한 전문 AI 이미지 편집 도구</t>
+  </si>
+  <si>
+    <t>https://www.adobe.com/products/photoshop/generative-fill.html</t>
+  </si>
+  <si>
+    <t>선택 영역과 레이어 기반이라 수정 범위를 정밀하게 통제하기 좋고 비파괴 편집 가능</t>
+  </si>
+  <si>
+    <t>유료 중심이며 Photoshop 기본 사용법을 알아야 장점을 살리기 쉬움</t>
+  </si>
+  <si>
+    <t>정밀 리터치, 합성, 배경 확장, 오브젝트 추가·삭제</t>
+  </si>
+  <si>
+    <t>Magnific (구 Freepik AI 계열)</t>
+  </si>
+  <si>
+    <t>이미지 생성과 자연어 편집, 고해상도 업스케일을 결합한 크리에이티브 AI 플랫폼</t>
+  </si>
+  <si>
+    <t>https://www.magnific.com/</t>
+  </si>
+  <si>
+    <t>업스케일·리터치·카메라 각도·스타일 변환 등 후편집 기능이 강함</t>
+  </si>
+  <si>
+    <t>고해상도·고급 모델 사용은 크레딧 소모가 크며 2026년 리브랜딩으로 명칭이 헷갈릴 수 있음</t>
+  </si>
+  <si>
+    <t>저해상도 이미지 개선, 사진 리터치, 스타일 변환, 생성 후 마무리</t>
+  </si>
+  <si>
+    <t>Genspark AI Image</t>
+  </si>
+  <si>
+    <t>Nano Banana, GPT Image, Ideogram, FLUX 등 여러 모델을 한곳에서 생성·편집할 수 있는 멀티모델 이미지 도구</t>
+  </si>
+  <si>
+    <t>https://www.genspark.ai/</t>
+  </si>
+  <si>
+    <t>여러 모델을 같은 서비스에서 비교할 수 있고 인페인트·아웃페인트·배경 제거·업스케일까지 연결됨</t>
+  </si>
+  <si>
+    <t>모델별 결과와 크레딧 규칙이 달라 비용/한도 파악이 필요</t>
+  </si>
+  <si>
+    <t>모델 비교, 이미지 생성과 편집을 한 화면에서 체험, 과제 비교 실험</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>게임·브랜드 자산용 이미지 생성과 스타일/캐릭터 맞춤 모델 학습에 특화된 크리에이티브 플랫폼</t>
+  </si>
+  <si>
+    <t>https://www.scenario.com/</t>
+  </si>
+  <si>
+    <t>일관된 스타일/캐릭터 자산 제작과 커스텀 모델, 팀·게임 파이프라인에 강함</t>
+  </si>
+  <si>
+    <t>일반 사진 생성만 할 때는 기능이 과하고, 무료 결과의 사용권 범위를 확인해야 함</t>
+  </si>
+  <si>
+    <t>게임 에셋, 캐릭터/아이템 세트, 브랜드 스타일 일관성</t>
+  </si>
+  <si>
+    <t>Playground AI</t>
+  </si>
+  <si>
+    <t>템플릿 기반 디자인과 여러 이미지 모델을 결합해 쉽게 생성·편집할 수 있는 웹 도구</t>
+  </si>
+  <si>
+    <t>https://playgroundai.com/</t>
+  </si>
+  <si>
+    <t>초보자가 쓰기 쉽고 템플릿/디자인 중심 작업에 빠르게 접근 가능</t>
+  </si>
+  <si>
+    <t>무료 모델 사용량이 적고 고해상도 편집은 상위 플랜 중심</t>
+  </si>
+  <si>
+    <t>SNS 이미지, 간단한 디자인, 모델별 이미지 생성 비교</t>
+  </si>
+  <si>
+    <t>Microsoft Designer</t>
+  </si>
+  <si>
+    <t>Microsoft 계정으로 이미지 생성, 오브젝트 지우기, 배경 제거·흐림, 디자인 제작을 쉽게 하는 AI 도구</t>
+  </si>
+  <si>
+    <t>https://designer.microsoft.com/</t>
+  </si>
+  <si>
+    <t>조작이 쉽고 이미지 생성과 카드·배너 등 디자인 제작이 함께 가능</t>
+  </si>
+  <si>
+    <t>무료 사용은 크레딧 제한이 있고 개인용 라이선스/사용 범위를 확인해야 함</t>
+  </si>
+  <si>
+    <t>간단한 포스터, 카드, 배너, 배경 제거·개체 지우기</t>
+  </si>
+  <si>
+    <t>Midjourney</t>
+  </si>
+  <si>
+    <t>감각적인 스타일과 높은 시각 완성도로 유명한 이미지 생성 AI로 웹 편집기를 통해 리프레임·리페인트도 지원</t>
+  </si>
+  <si>
+    <t>https://www.midjourney.com/</t>
+  </si>
+  <si>
+    <t>스타일·무드·컨셉 아트 품질이 높고 결과가 빠르게 '그럴듯하게' 나오는 편</t>
+  </si>
+  <si>
+    <t>무료 상시 플랜이 없고 세밀한 자연어 편집은 대화형 도구보다 익숙해지는 시간이 필요</t>
+  </si>
+  <si>
+    <t>컨셉 아트, 패션·광고 무드보드, 일러스트, 시네마틱 이미지</t>
+  </si>
+  <si>
+    <t>Ideogram</t>
+  </si>
+  <si>
+    <t>이미지 속 글자 표현과 로고·포스터에 강하며 Canvas에서 Magic Fill·Extend 편집을 제공하는 이미지 AI</t>
+  </si>
+  <si>
+    <t>https://ideogram.ai/</t>
+  </si>
+  <si>
+    <t>타이포그래피·로고·포스터에 강하고 Canvas에서 인페인트/아웃페인트 작업 가능</t>
+  </si>
+  <si>
+    <t>일부 편집 기능은 유료 플랜이 필요하고 무료 생성은 공개 범위/한도 확인 필요</t>
+  </si>
+  <si>
+    <t>텍스트가 들어가는 포스터, 로고, 브랜딩, 인페인트·아웃페인트</t>
+  </si>
+  <si>
+    <t>Recraft</t>
+  </si>
+  <si>
+    <t>사진뿐 아니라 벡터·아이콘·일러스트·목업까지 생성하고 수정할 수 있는 디자인 중심 이미지 AI</t>
+  </si>
+  <si>
+    <t>https://www.recraft.ai/</t>
+  </si>
+  <si>
+    <t>벡터 이미지와 아이콘·브랜드 그래픽, 목업 등 디자인 산출물에 강함</t>
+  </si>
+  <si>
+    <t>무료 플랜 결과의 소유권/공개 조건 등 라이선스 차이를 꼭 확인해야 함</t>
+  </si>
+  <si>
+    <t>아이콘, 벡터, 브랜드 그래픽, 목업, 일러스트</t>
+  </si>
+  <si>
+    <t>FLUX (Black Forest Labs Dev Playground)</t>
+  </si>
+  <si>
+    <t>Black Forest Labs의 FLUX 모델을 브라우저에서 직접 시험하고 이미지 편집까지 할 수 있는 개발자 플레이그라운드</t>
+  </si>
+  <si>
+    <t>https://dashboard.bfl.ai/</t>
+  </si>
+  <si>
+    <t>유료 중심</t>
+  </si>
+  <si>
+    <t>고품질 생성 모델과 편집 모델을 직접 선택하고 파라미터를 실험하기 좋음</t>
+  </si>
+  <si>
+    <t>크레딧 결제가 필요할 수 있고 일반 디자인 서비스보다 개발자 지향적</t>
+  </si>
+  <si>
+    <t>고품질 생성 비교, FLUX 모델 테스트, 이미지 편집 실험</t>
+  </si>
+  <si>
+    <t>ImageFX (Google Labs, 레거시)</t>
+  </si>
+  <si>
+    <t>Google Labs에서 제공되던 실험형 텍스트-이미지 생성 도구</t>
+  </si>
+  <si>
+    <t>https://labs.google/imagefx</t>
+  </si>
+  <si>
+    <t>무료(접근 상태 확인)</t>
+  </si>
+  <si>
+    <t>간단한 프롬프트 실험과 Google 이미지 생성 경험을 보기 쉬웠음</t>
+  </si>
+  <si>
+    <t>2026년 현재 labs.google/fx 중심 구성이 바뀌어 과제용 메인 테스트 서비스로는 불확실</t>
+  </si>
+  <si>
+    <t>레거시 사례 비교, Google 이미지 생성 서비스 변화 확인</t>
+  </si>
+  <si>
+    <t>Freepik AI (구 명칭/참고)</t>
+  </si>
+  <si>
+    <t>기존 Freepik AI Suite로 이미지 생성·편집·업스케일을 제공하던 크리에이티브 플랫폼</t>
+  </si>
+  <si>
+    <t>https://www.freepik.com/ai</t>
+  </si>
+  <si>
+    <t>생성·편집·업스케일·목업 등을 한곳에서 할 수 있고 다양한 외부 모델을 선택 가능</t>
+  </si>
+  <si>
+    <t>현재 Magnific와 서비스/브랜드가 겹쳐 중복 항목으로 볼 수 있음</t>
+  </si>
+  <si>
+    <t>과거 자료와 현재 서비스 비교, 통합형 크리에이티브 플랫폼 사례</t>
+  </si>
+  <si>
+    <t>클로바노트</t>
+  </si>
+  <si>
+    <t>https://clovanote.naver.com</t>
+  </si>
+  <si>
+    <t>다글로</t>
+  </si>
+  <si>
+    <t>https://daglo.ai</t>
+  </si>
+  <si>
+    <t>무료 사용량이 적어 자주 쓰면 유료 전환이 필요함</t>
+  </si>
+  <si>
+    <t>https://tiro.ooo</t>
+  </si>
+  <si>
+    <t>실시간 기록을 회의 중에 바로 보고 고칠 수 있음</t>
+  </si>
+  <si>
+    <t>무료 체험 시간이 짧고 이후 유료</t>
+  </si>
+  <si>
+    <t>팀 정기 회의 기록</t>
+  </si>
+  <si>
+    <t>에이닷 노트</t>
+  </si>
+  <si>
+    <t>https://adot.ai</t>
+  </si>
+  <si>
+    <t>무료</t>
+  </si>
+  <si>
+    <t>통화 녹음과 연동되고 무료 제공 범위가 넓은 편</t>
+  </si>
+  <si>
+    <t>Otter.ai</t>
+  </si>
+  <si>
+    <t>https://otter.ai</t>
+  </si>
+  <si>
+    <t>한국어 지원이 약하고 무료 플랜 녹음 시간이 짧음</t>
+  </si>
+  <si>
+    <t>Fireflies.ai</t>
+  </si>
+  <si>
+    <t>https://fireflies.ai</t>
+  </si>
+  <si>
+    <t>봇이 회의에 참석해 상대방이 부담을 느낄 수 있음</t>
+  </si>
+  <si>
+    <t>Fathom</t>
+  </si>
+  <si>
+    <t>https://fathom.video</t>
+  </si>
+  <si>
+    <t>비용 부담 없는 화상회의 기록</t>
+  </si>
+  <si>
+    <t>tl;dv</t>
+  </si>
+  <si>
+    <t>https://tldv.io</t>
+  </si>
+  <si>
+    <t>중요 순간을 타임스탬프로 표시하고 클립 공유가 쉬움</t>
+  </si>
+  <si>
+    <t>Tactiq</t>
+  </si>
+  <si>
+    <t>https://tactiq.io</t>
+  </si>
+  <si>
+    <t>봇 없이 브라우저에서 바로 기록됨</t>
+  </si>
+  <si>
+    <t>자막 기반이라 녹음 파일이 남지 않고 무료 회의 수 제한</t>
+  </si>
+  <si>
+    <t>가볍게 쓰는 화상회의 기록</t>
+  </si>
+  <si>
+    <t>Jamie</t>
+  </si>
+  <si>
+    <t>https://meetjamie.ai</t>
+  </si>
+  <si>
+    <t>무료 플랜 사용 시간이 적고 인지도가 낮음</t>
+  </si>
+  <si>
+    <t>Granola</t>
+  </si>
+  <si>
+    <t>https://granola.ai</t>
+  </si>
+  <si>
+    <t>영어 중심이고 팀 공유 기능은 유료</t>
+  </si>
+  <si>
+    <t>Read.ai</t>
+  </si>
+  <si>
+    <t>https://read.ai</t>
+  </si>
+  <si>
+    <t>분석 기능이 과하게 느껴질 수 있고 무료 한도가 적음</t>
+  </si>
+  <si>
+    <t>https://notion.so</t>
+  </si>
+  <si>
+    <t>노션 유료 요금제가 필요하고 노션 밖 활용이 불편</t>
+  </si>
+  <si>
+    <t>노션으로 일하는 팀</t>
+  </si>
+  <si>
+    <t>Zoom AI Companion</t>
+  </si>
+  <si>
+    <t>https://zoom.com</t>
+  </si>
+  <si>
+    <t>Microsoft Teams Copilot</t>
+  </si>
+  <si>
+    <t>Gemini in Google Meet</t>
+  </si>
+  <si>
+    <t>Krisp</t>
+  </si>
+  <si>
+    <t>https://krisp.ai</t>
+  </si>
+  <si>
+    <t>잡음 제거 품질이 뛰어나고 앱 상관없이 기록</t>
+  </si>
+  <si>
+    <t>노트 기능은 전문 회의록 도구보다 단순함</t>
+  </si>
+  <si>
+    <t>Plaud</t>
+  </si>
+  <si>
+    <t>https://plaud.ai</t>
+  </si>
+  <si>
+    <t>녹음 파일이나 받아쓴 텍스트를 회의록 형식으로 정리</t>
+  </si>
+  <si>
+    <t>자동 녹음 기능이 제한적이라 텍스트를 직접 넣어야 함</t>
+  </si>
+  <si>
+    <t>받아쓴 내용을 회의록 양식으로 다듬기</t>
+  </si>
+  <si>
+    <t>긴 회의 기록도 한 번에 넣어 정리할 수 있음</t>
+  </si>
+  <si>
+    <t>실시간 녹음 기능이 없어 받아쓴 텍스트가 필요함</t>
+  </si>
+  <si>
+    <t>회의록/기록</t>
+  </si>
+  <si>
+    <t>녹음하면 한국어 대화를 텍스트로 바꾸고 AI가 요약해 주는 네이버 서비스</t>
+  </si>
+  <si>
+    <t>한국어 인식 정확도가 높고 화자 구분·참여도 분석 제공</t>
+  </si>
+  <si>
+    <t>무료 변환 시간과 AI 요약 횟수에 월 한도가 있음</t>
+  </si>
+  <si>
+    <t>국내 회의·강의·인터뷰 기록</t>
+  </si>
+  <si>
+    <t>음성·영상 파일을 받아쓰고 요약하는 한국어 AI 기록 도구</t>
+  </si>
+  <si>
+    <t>한국어 받아쓰기 품질이 좋고 유튜브·영상 요약도 가능</t>
+  </si>
+  <si>
+    <t>강의 녹음, 인터뷰 정리</t>
+  </si>
+  <si>
+    <t>티로 (Tiro)</t>
+  </si>
+  <si>
+    <t>회의 중 실시간으로 기록하고 정리해 주는 AI 회의록</t>
+  </si>
+  <si>
+    <t>SK텔레콤의 AI 녹음·요약 서비스</t>
+  </si>
+  <si>
+    <t>에이닷 앱 생태계 중심이라 협업·외부 연동 기능이 적음</t>
+  </si>
+  <si>
+    <t>통화·개인 미팅 기록</t>
+  </si>
+  <si>
+    <t>실시간 받아쓰기와 요약을 해 주는 AI 회의 비서</t>
+  </si>
+  <si>
+    <t>실시간 자막, 팀원과 하이라이트·댓글 협업</t>
+  </si>
+  <si>
+    <t>영어 회의, 해외 팀 미팅</t>
+  </si>
+  <si>
+    <t>화상회의에 봇이 참석해 녹음·요약·검색을 해 주는 도구</t>
+  </si>
+  <si>
+    <t>CRM·Slack·Notion 등 연동이 많고 대화 검색이 강력함</t>
+  </si>
+  <si>
+    <t>영업 미팅, CRM 기록</t>
+  </si>
+  <si>
+    <t>Zoom·Meet·Teams 회의를 녹화하고 요약하는 AI 노트테이커</t>
+  </si>
+  <si>
+    <t>무료 플랜에서도 녹화·받아쓰기 무제한</t>
+  </si>
+  <si>
+    <t>고급 AI 요약·팀 기능은 유료, 한국어 품질은 영어보다 떨어짐</t>
+  </si>
+  <si>
+    <t>화상회의를 녹화해 타임스탬프·요약을 만드는 도구</t>
+  </si>
+  <si>
+    <t>무료 플랜은 AI 요약 횟수 제한이 있음</t>
+  </si>
+  <si>
+    <t>원격 팀 회의, 사용자 인터뷰</t>
+  </si>
+  <si>
+    <t>크롬 확장으로 Meet·Zoom 자막을 실시간 기록</t>
+  </si>
+  <si>
+    <t>봇 없이 기기 오디오를 받아 회의록을 만드는 AI</t>
+  </si>
+  <si>
+    <t>회의 봇이 필요 없어 오프라인·온라인 모두 기록 가능</t>
+  </si>
+  <si>
+    <t>대면 회의, 개인정보에 민감한 회의</t>
+  </si>
+  <si>
+    <t>내가 적은 메모에 AI가 회의 내용을 채워 넣는 노트앱</t>
+  </si>
+  <si>
+    <t>내 메모 스타일을 살려 깔끔한 회의록 완성, 봇 없음</t>
+  </si>
+  <si>
+    <t>1:1 미팅, 개인 업무 메모</t>
+  </si>
+  <si>
+    <t>회의 요약과 함께 참여도·분위기를 분석하는 AI</t>
+  </si>
+  <si>
+    <t>발언 비율·참여도 같은 회의 분석 지표 제공</t>
+  </si>
+  <si>
+    <t>회의 품질 개선, 팀 리더</t>
+  </si>
+  <si>
+    <t>Notion AI 회의 노트</t>
+  </si>
+  <si>
+    <t>노션 페이지 안에서 회의를 녹음·요약</t>
+  </si>
+  <si>
+    <t>유료(요금제)</t>
+  </si>
+  <si>
+    <t>회의록이 바로 노션 문서·할 일로 이어짐</t>
+  </si>
+  <si>
+    <t>Zoom에 내장된 회의 요약·질의응답 AI</t>
+  </si>
+  <si>
+    <t>유료(Zoom 유료 플랜)</t>
+  </si>
+  <si>
+    <t>별도 설치 없이 Zoom 회의 요약·후속 작업 자동 생성</t>
+  </si>
+  <si>
+    <t>Zoom 유료 계정 필요, Zoom 회의에만 사용 가능</t>
+  </si>
+  <si>
+    <t>Zoom 중심 회사</t>
+  </si>
+  <si>
+    <t>Teams 회의를 요약하고 결정사항·할 일을 정리</t>
+  </si>
+  <si>
+    <t>Teams·Outlook·Word와 바로 연동</t>
+  </si>
+  <si>
+    <t>M365 Copilot 유료 라이선스가 필요함</t>
+  </si>
+  <si>
+    <t>Teams를 쓰는 회사</t>
+  </si>
+  <si>
+    <t>Meet의 '메모 작성' 기능으로 회의록을 구글 문서로 저장</t>
+  </si>
+  <si>
+    <t>회의록이 구글 문서로 자동 저장·공유됨</t>
+  </si>
+  <si>
+    <t>워크스페이스 유료 요금제 필요, 한국어 지원 범위 확인 필요</t>
+  </si>
+  <si>
+    <t>소음 제거와 AI 회의 노트를 함께 제공</t>
+  </si>
+  <si>
+    <t>재택근무, 시끄러운 환경의 회의</t>
+  </si>
+  <si>
+    <t>녹음기 기기와 앱으로 대면 대화를 기록·요약</t>
+  </si>
+  <si>
+    <t>기기 구매 + 부분 무료</t>
+  </si>
+  <si>
+    <t>휴대용 녹음기라 대면 회의·통화 기록이 편함</t>
+  </si>
+  <si>
+    <t>기기 구매가 필요하고 AI 사용 시간 초과 시 구독 필요</t>
+  </si>
+  <si>
+    <t>대면 미팅, 현장 기록</t>
+  </si>
+  <si>
+    <t>원하는 양식(결정사항·할 일 등)으로 자유롭게 정리</t>
+  </si>
+  <si>
+    <t>긴 회의 기록을 요약하고 결정사항·할 일 정리</t>
+  </si>
+  <si>
+    <t>긴 회의록 요약, 보고서 변환</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1470,13 +2177,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color theme="10"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1776,7 +2478,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1903,22 +2605,18 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="44">
     <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1937,6 +2635,7 @@
     <cellStyle name="60% - 강조색4" xfId="33" builtinId="44" customBuiltin="1"/>
     <cellStyle name="60% - 강조색5" xfId="37" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% - 강조색6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="42" xr:uid="{1BBFC466-AD07-49DD-8FFB-8157AD87D069}"/>
     <cellStyle name="강조색1" xfId="18" builtinId="29" customBuiltin="1"/>
     <cellStyle name="강조색2" xfId="22" builtinId="33" customBuiltin="1"/>
     <cellStyle name="강조색3" xfId="26" builtinId="37" customBuiltin="1"/>
@@ -1961,7 +2660,7 @@
     <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="42" builtinId="8"/>
+    <cellStyle name="표준 2" xfId="43" xr:uid="{AF015FE8-4228-449F-9703-312B44194C80}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2273,8 +2972,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J62"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:J100"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="26.09765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.3984375" bestFit="1" customWidth="1"/>
@@ -2283,7 +2982,7 @@
     <col min="9" max="9" width="15.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2312,7 +3011,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2338,7 +3037,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -2364,7 +3063,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -2390,7 +3089,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -2416,7 +3115,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -2442,7 +3141,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -2468,7 +3167,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>52</v>
       </c>
@@ -2494,7 +3193,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -2520,7 +3219,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>65</v>
       </c>
@@ -2546,7 +3245,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>72</v>
       </c>
@@ -2572,7 +3271,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>79</v>
       </c>
@@ -2598,7 +3297,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>86</v>
       </c>
@@ -2627,7 +3326,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>94</v>
       </c>
@@ -2656,7 +3355,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>102</v>
       </c>
@@ -2685,7 +3384,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>110</v>
       </c>
@@ -2714,7 +3413,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>118</v>
       </c>
@@ -2743,7 +3442,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -2772,7 +3471,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>136</v>
       </c>
@@ -2801,7 +3500,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>144</v>
       </c>
@@ -2830,7 +3529,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>152</v>
       </c>
@@ -2859,7 +3558,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>160</v>
       </c>
@@ -2888,7 +3587,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>168</v>
       </c>
@@ -2917,7 +3616,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>177</v>
       </c>
@@ -2946,7 +3645,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>185</v>
       </c>
@@ -2975,7 +3674,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>193</v>
       </c>
@@ -3004,7 +3703,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>201</v>
       </c>
@@ -3033,1059 +3732,2053 @@
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:10">
+      <c r="A28" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2" t="s">
+      <c r="I28" s="1"/>
+      <c r="J28" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:10">
+      <c r="A29" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="H29" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2" t="s">
+      <c r="I29" s="1"/>
+      <c r="J29" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A30" s="2" t="s">
+    <row r="30" spans="1:10">
+      <c r="A30" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H30" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2" t="s">
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A31" s="2" t="s">
+    <row r="31" spans="1:10">
+      <c r="A31" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H31" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2" t="s">
+      <c r="I31" s="1"/>
+      <c r="J31" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:10">
+      <c r="A32" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2" t="s">
+      <c r="I32" s="1"/>
+      <c r="J32" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:10">
+      <c r="A33" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2" t="s">
+      <c r="I33" s="1"/>
+      <c r="J33" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:10">
+      <c r="A34" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H34" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2" t="s">
+      <c r="I34" s="1"/>
+      <c r="J34" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:10">
+      <c r="A35" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2" t="s">
+      <c r="I35" s="1"/>
+      <c r="J35" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:10">
+      <c r="A36" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H36" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2" t="s">
+      <c r="I36" s="1"/>
+      <c r="J36" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:10">
+      <c r="A37" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="H37" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2" t="s">
+      <c r="I37" s="1"/>
+      <c r="J37" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:10">
+      <c r="A38" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H38" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2" t="s">
+      <c r="I38" s="1"/>
+      <c r="J38" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A39" s="2" t="s">
+    <row r="39" spans="1:10">
+      <c r="A39" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="H39" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2" t="s">
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A40" s="2" t="s">
+    <row r="40" spans="1:10">
+      <c r="A40" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="H40" s="2" t="s">
+      <c r="H40" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2" t="s">
+      <c r="I40" s="1"/>
+      <c r="J40" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A41" s="2" t="s">
+    <row r="41" spans="1:10">
+      <c r="A41" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="H41" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2" t="s">
+      <c r="I41" s="1"/>
+      <c r="J41" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A42" s="2" t="s">
+    <row r="42" spans="1:10">
+      <c r="A42" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G42" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="H42" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2" t="s">
+      <c r="I42" s="1"/>
+      <c r="J42" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A43" s="2" t="s">
+    <row r="43" spans="1:10">
+      <c r="A43" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="H43" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2" t="s">
+      <c r="I43" s="1"/>
+      <c r="J43" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A44" s="2" t="s">
+    <row r="44" spans="1:10">
+      <c r="A44" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="H44" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2" t="s">
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A45" s="2" t="s">
+    <row r="45" spans="1:10">
+      <c r="A45" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="H45" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2" t="s">
+      <c r="I45" s="1"/>
+      <c r="J45" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A46" s="2" t="s">
+    <row r="46" spans="1:10">
+      <c r="A46" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G46" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="H46" s="2" t="s">
+      <c r="H46" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2" t="s">
+      <c r="I46" s="1"/>
+      <c r="J46" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A47" s="2" t="s">
+    <row r="47" spans="1:10">
+      <c r="A47" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G47" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="H47" s="2" t="s">
+      <c r="H47" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2" t="s">
+      <c r="I47" s="1"/>
+      <c r="J47" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A48" s="2" t="s">
+    <row r="48" spans="1:10">
+      <c r="A48" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F48" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="G48" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="H48" s="2" t="s">
+      <c r="H48" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2" t="s">
+      <c r="I48" s="1"/>
+      <c r="J48" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A49" s="2" t="s">
+    <row r="49" spans="1:10">
+      <c r="A49" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="G49" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="H49" s="2" t="s">
+      <c r="H49" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2" t="s">
+      <c r="I49" s="1"/>
+      <c r="J49" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A50" s="2" t="s">
+    <row r="50" spans="1:10">
+      <c r="A50" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="G50" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="H50" s="2" t="s">
+      <c r="H50" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2" t="s">
+      <c r="I50" s="1"/>
+      <c r="J50" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A51" s="2" t="s">
+    <row r="51" spans="1:10">
+      <c r="A51" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="G51" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="H51" s="2" t="s">
+      <c r="H51" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2" t="s">
+      <c r="I51" s="1"/>
+      <c r="J51" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A52" s="2" t="s">
+    <row r="52" spans="1:10">
+      <c r="A52" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="H52" s="2" t="s">
+      <c r="H52" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2" t="s">
+      <c r="I52" s="1"/>
+      <c r="J52" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A53" s="2" t="s">
+    <row r="53" spans="1:10">
+      <c r="A53" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="F53" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="H53" s="2" t="s">
+      <c r="H53" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2" t="s">
+      <c r="I53" s="1"/>
+      <c r="J53" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A54" s="2" t="s">
+    <row r="54" spans="1:10">
+      <c r="A54" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E54" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F54" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="G54" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="H54" s="2" t="s">
+      <c r="H54" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2" t="s">
+      <c r="I54" s="1"/>
+      <c r="J54" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A55" s="2" t="s">
+    <row r="55" spans="1:10">
+      <c r="A55" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E55" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="H55" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2" t="s">
+      <c r="I55" s="1"/>
+      <c r="J55" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A56" s="2" t="s">
+    <row r="56" spans="1:10">
+      <c r="A56" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F56" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="G56" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="H56" s="2" t="s">
+      <c r="H56" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2" t="s">
+      <c r="I56" s="1"/>
+      <c r="J56" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A57" s="2" t="s">
+    <row r="57" spans="1:10">
+      <c r="A57" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="F57" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G57" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="H57" s="2" t="s">
+      <c r="H57" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2" t="s">
+      <c r="I57" s="1"/>
+      <c r="J57" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A58" s="2" t="s">
+    <row r="58" spans="1:10">
+      <c r="A58" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E58" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F58" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G58" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="H58" s="2" t="s">
+      <c r="H58" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2" t="s">
+      <c r="I58" s="1"/>
+      <c r="J58" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A59" s="2" t="s">
+    <row r="59" spans="1:10">
+      <c r="A59" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E59" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="F59" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G59" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="H59" s="2" t="s">
+      <c r="H59" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2" t="s">
+      <c r="I59" s="1"/>
+      <c r="J59" s="1" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A60" s="2" t="s">
+    <row r="60" spans="1:10">
+      <c r="A60" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E60" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="F60" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G60" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="H60" s="2" t="s">
+      <c r="H60" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2" t="s">
+      <c r="I60" s="1"/>
+      <c r="J60" s="1" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A61" s="2" t="s">
+    <row r="61" spans="1:10">
+      <c r="A61" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E61" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="F61" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="H61" s="2" t="s">
+      <c r="H61" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2" t="s">
+      <c r="I61" s="1"/>
+      <c r="J61" s="1" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>230</v>
+        <v>424</v>
       </c>
       <c r="B62" t="s">
-        <v>210</v>
+        <v>425</v>
       </c>
       <c r="C62" t="s">
-        <v>231</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
+      </c>
+      <c r="D62" t="s">
+        <v>427</v>
       </c>
       <c r="E62" t="s">
+        <v>428</v>
+      </c>
+      <c r="F62" t="s">
+        <v>429</v>
+      </c>
+      <c r="G62" t="s">
+        <v>430</v>
+      </c>
+      <c r="H62" t="s">
+        <v>431</v>
+      </c>
+      <c r="I62" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>433</v>
+      </c>
+      <c r="B63" t="s">
+        <v>425</v>
+      </c>
+      <c r="C63" t="s">
+        <v>434</v>
+      </c>
+      <c r="D63" t="s">
+        <v>435</v>
+      </c>
+      <c r="E63" t="s">
+        <v>428</v>
+      </c>
+      <c r="F63" t="s">
+        <v>436</v>
+      </c>
+      <c r="G63" t="s">
+        <v>437</v>
+      </c>
+      <c r="H63" t="s">
+        <v>438</v>
+      </c>
+      <c r="I63" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>439</v>
+      </c>
+      <c r="B64" t="s">
+        <v>425</v>
+      </c>
+      <c r="C64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D64" t="s">
+        <v>441</v>
+      </c>
+      <c r="E64" t="s">
+        <v>428</v>
+      </c>
+      <c r="F64" t="s">
+        <v>442</v>
+      </c>
+      <c r="G64" t="s">
+        <v>443</v>
+      </c>
+      <c r="H64" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" t="s">
+        <v>445</v>
+      </c>
+      <c r="B65" t="s">
+        <v>425</v>
+      </c>
+      <c r="C65" t="s">
+        <v>446</v>
+      </c>
+      <c r="D65" t="s">
+        <v>447</v>
+      </c>
+      <c r="E65" t="s">
+        <v>428</v>
+      </c>
+      <c r="F65" t="s">
+        <v>448</v>
+      </c>
+      <c r="G65" t="s">
+        <v>449</v>
+      </c>
+      <c r="H65" t="s">
+        <v>450</v>
+      </c>
+      <c r="I65" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" t="s">
+        <v>452</v>
+      </c>
+      <c r="B66" t="s">
+        <v>425</v>
+      </c>
+      <c r="C66" t="s">
+        <v>453</v>
+      </c>
+      <c r="D66" t="s">
+        <v>454</v>
+      </c>
+      <c r="E66" t="s">
+        <v>428</v>
+      </c>
+      <c r="F66" t="s">
+        <v>455</v>
+      </c>
+      <c r="G66" t="s">
+        <v>456</v>
+      </c>
+      <c r="H66" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" t="s">
+        <v>458</v>
+      </c>
+      <c r="B67" t="s">
+        <v>425</v>
+      </c>
+      <c r="C67" t="s">
+        <v>459</v>
+      </c>
+      <c r="D67" t="s">
+        <v>460</v>
+      </c>
+      <c r="E67" t="s">
+        <v>428</v>
+      </c>
+      <c r="F67" t="s">
+        <v>461</v>
+      </c>
+      <c r="G67" t="s">
+        <v>462</v>
+      </c>
+      <c r="H67" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" t="s">
+        <v>464</v>
+      </c>
+      <c r="B68" t="s">
+        <v>425</v>
+      </c>
+      <c r="C68" t="s">
+        <v>465</v>
+      </c>
+      <c r="D68" t="s">
+        <v>466</v>
+      </c>
+      <c r="E68" t="s">
+        <v>428</v>
+      </c>
+      <c r="F68" t="s">
+        <v>467</v>
+      </c>
+      <c r="G68" t="s">
+        <v>468</v>
+      </c>
+      <c r="H68" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" t="s">
+        <v>470</v>
+      </c>
+      <c r="B69" t="s">
+        <v>425</v>
+      </c>
+      <c r="C69" t="s">
+        <v>471</v>
+      </c>
+      <c r="D69" t="s">
+        <v>472</v>
+      </c>
+      <c r="E69" t="s">
+        <v>389</v>
+      </c>
+      <c r="F69" t="s">
+        <v>473</v>
+      </c>
+      <c r="G69" t="s">
+        <v>474</v>
+      </c>
+      <c r="H69" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" t="s">
+        <v>476</v>
+      </c>
+      <c r="B70" t="s">
+        <v>425</v>
+      </c>
+      <c r="C70" t="s">
+        <v>477</v>
+      </c>
+      <c r="D70" t="s">
+        <v>478</v>
+      </c>
+      <c r="E70" t="s">
+        <v>428</v>
+      </c>
+      <c r="F70" t="s">
+        <v>479</v>
+      </c>
+      <c r="G70" t="s">
+        <v>480</v>
+      </c>
+      <c r="H70" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
+        <v>482</v>
+      </c>
+      <c r="B71" t="s">
+        <v>425</v>
+      </c>
+      <c r="C71" t="s">
+        <v>483</v>
+      </c>
+      <c r="D71" t="s">
+        <v>484</v>
+      </c>
+      <c r="E71" t="s">
+        <v>428</v>
+      </c>
+      <c r="F71" t="s">
+        <v>485</v>
+      </c>
+      <c r="G71" t="s">
+        <v>486</v>
+      </c>
+      <c r="H71" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" t="s">
+        <v>488</v>
+      </c>
+      <c r="B72" t="s">
+        <v>425</v>
+      </c>
+      <c r="C72" t="s">
+        <v>489</v>
+      </c>
+      <c r="D72" t="s">
+        <v>490</v>
+      </c>
+      <c r="E72" t="s">
+        <v>428</v>
+      </c>
+      <c r="F72" t="s">
+        <v>491</v>
+      </c>
+      <c r="G72" t="s">
+        <v>492</v>
+      </c>
+      <c r="H72" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" t="s">
+        <v>494</v>
+      </c>
+      <c r="B73" t="s">
+        <v>425</v>
+      </c>
+      <c r="C73" t="s">
+        <v>495</v>
+      </c>
+      <c r="D73" t="s">
+        <v>496</v>
+      </c>
+      <c r="E73" t="s">
+        <v>428</v>
+      </c>
+      <c r="F73" t="s">
+        <v>497</v>
+      </c>
+      <c r="G73" t="s">
+        <v>498</v>
+      </c>
+      <c r="H73" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" t="s">
+        <v>500</v>
+      </c>
+      <c r="B74" t="s">
+        <v>425</v>
+      </c>
+      <c r="C74" t="s">
+        <v>501</v>
+      </c>
+      <c r="D74" t="s">
+        <v>502</v>
+      </c>
+      <c r="E74" t="s">
+        <v>428</v>
+      </c>
+      <c r="F74" t="s">
+        <v>503</v>
+      </c>
+      <c r="G74" t="s">
+        <v>504</v>
+      </c>
+      <c r="H74" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" t="s">
+        <v>506</v>
+      </c>
+      <c r="B75" t="s">
+        <v>425</v>
+      </c>
+      <c r="C75" t="s">
+        <v>507</v>
+      </c>
+      <c r="D75" t="s">
+        <v>508</v>
+      </c>
+      <c r="E75" t="s">
+        <v>389</v>
+      </c>
+      <c r="F75" t="s">
+        <v>509</v>
+      </c>
+      <c r="G75" t="s">
+        <v>510</v>
+      </c>
+      <c r="H75" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" t="s">
+        <v>512</v>
+      </c>
+      <c r="B76" t="s">
+        <v>425</v>
+      </c>
+      <c r="C76" t="s">
+        <v>513</v>
+      </c>
+      <c r="D76" t="s">
+        <v>514</v>
+      </c>
+      <c r="E76" t="s">
+        <v>428</v>
+      </c>
+      <c r="F76" t="s">
+        <v>515</v>
+      </c>
+      <c r="G76" t="s">
+        <v>516</v>
+      </c>
+      <c r="H76" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" t="s">
+        <v>518</v>
+      </c>
+      <c r="B77" t="s">
+        <v>425</v>
+      </c>
+      <c r="C77" t="s">
+        <v>519</v>
+      </c>
+      <c r="D77" t="s">
+        <v>520</v>
+      </c>
+      <c r="E77" t="s">
+        <v>428</v>
+      </c>
+      <c r="F77" t="s">
+        <v>521</v>
+      </c>
+      <c r="G77" t="s">
+        <v>522</v>
+      </c>
+      <c r="H77" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" t="s">
+        <v>524</v>
+      </c>
+      <c r="B78" t="s">
+        <v>425</v>
+      </c>
+      <c r="C78" t="s">
+        <v>525</v>
+      </c>
+      <c r="D78" t="s">
+        <v>526</v>
+      </c>
+      <c r="E78" t="s">
+        <v>527</v>
+      </c>
+      <c r="F78" t="s">
+        <v>528</v>
+      </c>
+      <c r="G78" t="s">
+        <v>529</v>
+      </c>
+      <c r="H78" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" t="s">
+        <v>531</v>
+      </c>
+      <c r="B79" t="s">
+        <v>425</v>
+      </c>
+      <c r="C79" t="s">
+        <v>532</v>
+      </c>
+      <c r="D79" t="s">
+        <v>533</v>
+      </c>
+      <c r="E79" t="s">
+        <v>534</v>
+      </c>
+      <c r="F79" t="s">
+        <v>535</v>
+      </c>
+      <c r="G79" t="s">
+        <v>536</v>
+      </c>
+      <c r="H79" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" t="s">
+        <v>538</v>
+      </c>
+      <c r="B80" t="s">
+        <v>425</v>
+      </c>
+      <c r="C80" t="s">
+        <v>539</v>
+      </c>
+      <c r="D80" t="s">
+        <v>540</v>
+      </c>
+      <c r="E80" t="s">
+        <v>428</v>
+      </c>
+      <c r="F80" t="s">
+        <v>541</v>
+      </c>
+      <c r="G80" t="s">
+        <v>542</v>
+      </c>
+      <c r="H80" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>544</v>
+      </c>
+      <c r="B81" t="s">
+        <v>601</v>
+      </c>
+      <c r="C81" t="s">
+        <v>602</v>
+      </c>
+      <c r="D81" t="s">
+        <v>545</v>
+      </c>
+      <c r="E81" t="s">
         <v>213</v>
       </c>
-      <c r="F62" t="s">
-        <v>233</v>
-      </c>
-      <c r="H62" t="s">
-        <v>425</v>
-      </c>
-      <c r="J62" t="s">
-        <v>217</v>
+      <c r="F81" t="s">
+        <v>603</v>
+      </c>
+      <c r="G81" t="s">
+        <v>604</v>
+      </c>
+      <c r="H81" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>546</v>
+      </c>
+      <c r="B82" t="s">
+        <v>601</v>
+      </c>
+      <c r="C82" t="s">
+        <v>606</v>
+      </c>
+      <c r="D82" t="s">
+        <v>547</v>
+      </c>
+      <c r="E82" t="s">
+        <v>213</v>
+      </c>
+      <c r="F82" t="s">
+        <v>607</v>
+      </c>
+      <c r="G82" t="s">
+        <v>548</v>
+      </c>
+      <c r="H82" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>609</v>
+      </c>
+      <c r="B83" t="s">
+        <v>601</v>
+      </c>
+      <c r="C83" t="s">
+        <v>610</v>
+      </c>
+      <c r="D83" t="s">
+        <v>549</v>
+      </c>
+      <c r="E83" t="s">
+        <v>239</v>
+      </c>
+      <c r="F83" t="s">
+        <v>550</v>
+      </c>
+      <c r="G83" t="s">
+        <v>551</v>
+      </c>
+      <c r="H83" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>553</v>
+      </c>
+      <c r="B84" t="s">
+        <v>601</v>
+      </c>
+      <c r="C84" t="s">
+        <v>611</v>
+      </c>
+      <c r="D84" t="s">
+        <v>554</v>
+      </c>
+      <c r="E84" t="s">
+        <v>555</v>
+      </c>
+      <c r="F84" t="s">
+        <v>556</v>
+      </c>
+      <c r="G84" t="s">
+        <v>612</v>
+      </c>
+      <c r="H84" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>557</v>
+      </c>
+      <c r="B85" t="s">
+        <v>601</v>
+      </c>
+      <c r="C85" t="s">
+        <v>614</v>
+      </c>
+      <c r="D85" t="s">
+        <v>558</v>
+      </c>
+      <c r="E85" t="s">
+        <v>213</v>
+      </c>
+      <c r="F85" t="s">
+        <v>615</v>
+      </c>
+      <c r="G85" t="s">
+        <v>559</v>
+      </c>
+      <c r="H85" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>560</v>
+      </c>
+      <c r="B86" t="s">
+        <v>601</v>
+      </c>
+      <c r="C86" t="s">
+        <v>617</v>
+      </c>
+      <c r="D86" t="s">
+        <v>561</v>
+      </c>
+      <c r="E86" t="s">
+        <v>213</v>
+      </c>
+      <c r="F86" t="s">
+        <v>618</v>
+      </c>
+      <c r="G86" t="s">
+        <v>562</v>
+      </c>
+      <c r="H86" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>563</v>
+      </c>
+      <c r="B87" t="s">
+        <v>601</v>
+      </c>
+      <c r="C87" t="s">
+        <v>620</v>
+      </c>
+      <c r="D87" t="s">
+        <v>564</v>
+      </c>
+      <c r="E87" t="s">
+        <v>213</v>
+      </c>
+      <c r="F87" t="s">
+        <v>621</v>
+      </c>
+      <c r="G87" t="s">
+        <v>622</v>
+      </c>
+      <c r="H87" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>566</v>
+      </c>
+      <c r="B88" t="s">
+        <v>601</v>
+      </c>
+      <c r="C88" t="s">
+        <v>623</v>
+      </c>
+      <c r="D88" t="s">
+        <v>567</v>
+      </c>
+      <c r="E88" t="s">
+        <v>213</v>
+      </c>
+      <c r="F88" t="s">
+        <v>568</v>
+      </c>
+      <c r="G88" t="s">
+        <v>624</v>
+      </c>
+      <c r="H88" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>569</v>
+      </c>
+      <c r="B89" t="s">
+        <v>601</v>
+      </c>
+      <c r="C89" t="s">
+        <v>626</v>
+      </c>
+      <c r="D89" t="s">
+        <v>570</v>
+      </c>
+      <c r="E89" t="s">
+        <v>213</v>
+      </c>
+      <c r="F89" t="s">
+        <v>571</v>
+      </c>
+      <c r="G89" t="s">
+        <v>572</v>
+      </c>
+      <c r="H89" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
+        <v>574</v>
+      </c>
+      <c r="B90" t="s">
+        <v>601</v>
+      </c>
+      <c r="C90" t="s">
+        <v>627</v>
+      </c>
+      <c r="D90" t="s">
+        <v>575</v>
+      </c>
+      <c r="E90" t="s">
+        <v>213</v>
+      </c>
+      <c r="F90" t="s">
+        <v>628</v>
+      </c>
+      <c r="G90" t="s">
+        <v>576</v>
+      </c>
+      <c r="H90" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>577</v>
+      </c>
+      <c r="B91" t="s">
+        <v>601</v>
+      </c>
+      <c r="C91" t="s">
+        <v>630</v>
+      </c>
+      <c r="D91" t="s">
+        <v>578</v>
+      </c>
+      <c r="E91" t="s">
+        <v>213</v>
+      </c>
+      <c r="F91" t="s">
+        <v>631</v>
+      </c>
+      <c r="G91" t="s">
+        <v>579</v>
+      </c>
+      <c r="H91" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
+        <v>580</v>
+      </c>
+      <c r="B92" t="s">
+        <v>601</v>
+      </c>
+      <c r="C92" t="s">
+        <v>633</v>
+      </c>
+      <c r="D92" t="s">
+        <v>581</v>
+      </c>
+      <c r="E92" t="s">
+        <v>213</v>
+      </c>
+      <c r="F92" t="s">
+        <v>634</v>
+      </c>
+      <c r="G92" t="s">
+        <v>582</v>
+      </c>
+      <c r="H92" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
+        <v>636</v>
+      </c>
+      <c r="B93" t="s">
+        <v>601</v>
+      </c>
+      <c r="C93" t="s">
+        <v>637</v>
+      </c>
+      <c r="D93" t="s">
+        <v>583</v>
+      </c>
+      <c r="E93" t="s">
+        <v>638</v>
+      </c>
+      <c r="F93" t="s">
+        <v>639</v>
+      </c>
+      <c r="G93" t="s">
+        <v>584</v>
+      </c>
+      <c r="H93" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>586</v>
+      </c>
+      <c r="B94" t="s">
+        <v>601</v>
+      </c>
+      <c r="C94" t="s">
+        <v>640</v>
+      </c>
+      <c r="D94" t="s">
+        <v>587</v>
+      </c>
+      <c r="E94" t="s">
+        <v>641</v>
+      </c>
+      <c r="F94" t="s">
+        <v>642</v>
+      </c>
+      <c r="G94" t="s">
+        <v>643</v>
+      </c>
+      <c r="H94" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>588</v>
+      </c>
+      <c r="B95" t="s">
+        <v>601</v>
+      </c>
+      <c r="C95" t="s">
+        <v>645</v>
+      </c>
+      <c r="D95" t="s">
+        <v>299</v>
+      </c>
+      <c r="E95" t="s">
+        <v>300</v>
+      </c>
+      <c r="F95" t="s">
+        <v>646</v>
+      </c>
+      <c r="G95" t="s">
+        <v>647</v>
+      </c>
+      <c r="H95" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>589</v>
+      </c>
+      <c r="B96" t="s">
+        <v>601</v>
+      </c>
+      <c r="C96" t="s">
+        <v>649</v>
+      </c>
+      <c r="D96" t="s">
+        <v>307</v>
+      </c>
+      <c r="E96" t="s">
+        <v>308</v>
+      </c>
+      <c r="F96" t="s">
+        <v>650</v>
+      </c>
+      <c r="G96" t="s">
+        <v>651</v>
+      </c>
+      <c r="H96" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>590</v>
+      </c>
+      <c r="B97" t="s">
+        <v>601</v>
+      </c>
+      <c r="C97" t="s">
+        <v>652</v>
+      </c>
+      <c r="D97" t="s">
+        <v>591</v>
+      </c>
+      <c r="E97" t="s">
+        <v>213</v>
+      </c>
+      <c r="F97" t="s">
+        <v>592</v>
+      </c>
+      <c r="G97" t="s">
+        <v>593</v>
+      </c>
+      <c r="H97" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>594</v>
+      </c>
+      <c r="B98" t="s">
+        <v>601</v>
+      </c>
+      <c r="C98" t="s">
+        <v>654</v>
+      </c>
+      <c r="D98" t="s">
+        <v>595</v>
+      </c>
+      <c r="E98" t="s">
+        <v>655</v>
+      </c>
+      <c r="F98" t="s">
+        <v>656</v>
+      </c>
+      <c r="G98" t="s">
+        <v>657</v>
+      </c>
+      <c r="H98" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>412</v>
+      </c>
+      <c r="B99" t="s">
+        <v>601</v>
+      </c>
+      <c r="C99" t="s">
+        <v>596</v>
+      </c>
+      <c r="D99" t="s">
+        <v>414</v>
+      </c>
+      <c r="E99" t="s">
+        <v>213</v>
+      </c>
+      <c r="F99" t="s">
+        <v>659</v>
+      </c>
+      <c r="G99" t="s">
+        <v>597</v>
+      </c>
+      <c r="H99" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>405</v>
+      </c>
+      <c r="B100" t="s">
+        <v>601</v>
+      </c>
+      <c r="C100" t="s">
+        <v>660</v>
+      </c>
+      <c r="D100" t="s">
+        <v>407</v>
+      </c>
+      <c r="E100" t="s">
+        <v>213</v>
+      </c>
+      <c r="F100" t="s">
+        <v>599</v>
+      </c>
+      <c r="G100" t="s">
+        <v>600</v>
+      </c>
+      <c r="H100" t="s">
+        <v>661</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{9A33205E-DC14-4D4E-AABE-AE049ADA6BB7}"/>
   <phoneticPr fontId="18" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="D62" r:id="rId1" xr:uid="{0E382258-CB96-41B8-8472-CF7481691F0C}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>